--- a/pilot/review/legacy_fields_review.xlsx
+++ b/pilot/review/legacy_fields_review.xlsx
@@ -36,7 +36,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -46,11 +46,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8EEF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,13 +61,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -476,14 +468,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  대응 없음 (4)             팀이 정할 것: file_id(영상·이미지 파일 참조)를 v2 에 둘지. ← 노란 칸</t>
+          <t xml:space="preserve">  대응 없음 (0)             남은 결정 없음</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  제외(사유 기록) (6)        v2 에 두지 않기로 한 것과 이유</t>
+          <t xml:space="preserve">  제외(사유 기록) (10)        v2 에 두지 않기로 한 것과 이유</t>
         </is>
       </c>
     </row>
@@ -526,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -569,102 +561,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>LUNG_CANCER.file_id</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>이미지 및 영상 파일에 대한 외래키이다.</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>LUNG_CRF</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>영상·이미지 파일 참조. v1 은 파일 외래키를 두었으나 v2 저장 구조에는 파일 표가 없다 — 코호트 DB 가 영상 파일을 담는지부터 정해야 한다</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>LYMPHOMA.file_id</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>PET/CT, CT, MRI 또는 병리 이미지 파일의 외래키이다.</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>PATHOLOGY_REPORT</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>영상·이미지 파일 참조. v1 은 파일 외래키를 두었으나 v2 저장 구조에는 파일 표가 없다 — 코호트 DB 가 영상 파일을 담는지부터 정해야 한다</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>BREAST_CANCER.file_id</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>이미지 및 영상 파일에 대한 외래키이다.</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>BREAST_CRF</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>영상·이미지 파일 참조. v1 은 파일 외래키를 두었으나 v2 저장 구조에는 파일 표가 없다 — 코호트 DB 가 영상 파일을 담는지부터 정해야 한다</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>MASLD.file_id</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>이미지/영상 파일 ID</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>MASLD_CRF</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>영상·이미지 파일 참조. v1 은 파일 외래키를 두었으나 v2 저장 구조에는 파일 표가 없다 — 코호트 DB 가 영상 파일을 담는지부터 정해야 한다</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -676,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -712,34 +608,34 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>COLORECTAL_CANCER.impt_read_ymd</t>
+          <t>LUNG_CANCER.file_id</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>면역조직화학병리 조직을 판독한 연월일이다.</t>
+          <t>이미지 및 영상 파일에 대한 외래키이다.</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>PATHOLOGY_REPORT</t>
+          <t>LUNG_CRF</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>병리 판독일. v2 는 검체 채취일만 둔다 — 판독 소요일이 필요해지면 PATHOLOGY_REPORT 에 report_date 를 더한다</t>
+          <t>영상·이미지 파일 참조. 코호트 DB 는 영상 파일을 담지 않는다 (2026-09-21 결정). 담게 되면 IMAGE 확장 표를 둔다</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>COLORECTAL_CANCER.mlpt_read_ymd</t>
+          <t>COLORECTAL_CANCER.impt_read_ymd</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>분자병리 조직을 판독한 연월일이다.</t>
+          <t>면역조직화학병리 조직을 판독한 연월일이다.</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -749,19 +645,19 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>병리 판독일. 위와 같다</t>
+          <t>병리 판독일. v2 는 검체 채취일만 둔다 — 판독 소요일이 필요해지면 PATHOLOGY_REPORT 에 report_date 를 더한다</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>COLORECTAL_CANCER.bpsy_read_ymd</t>
+          <t>COLORECTAL_CANCER.mlpt_read_ymd</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>생체검사 조직을 판독한 연월일이다.</t>
+          <t>분자병리 조직을 판독한 연월일이다.</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -778,12 +674,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>COLORECTAL_CANCER.ohad_hstr_yn_noans_spcd</t>
+          <t>COLORECTAL_CANCER.bpsy_read_ymd</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>타병원 진단 후 전원 여부를 나타내는 코드값이다.</t>
+          <t>생체검사 조직을 판독한 연월일이다.</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -793,51 +689,139 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>타병원 진단 후 전원 여부. 코호트 정의 항목이 아니며 필요하면 OBSERVATION 한 개념으로 받는다</t>
+          <t>병리 판독일. 위와 같다</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>MASLD.procedure_occurrence_crtn_dt</t>
+          <t>COLORECTAL_CANCER.ohad_hstr_yn_noans_spcd</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>행위처방 데이터 생성일시이다.</t>
+          <t>타병원 진단 후 전원 여부를 나타내는 코드값이다.</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>BIOMARKER</t>
+          <t>PATHOLOGY_REPORT</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>행위처방 레코드의 생성 일시. 임상 값이 아니라 원천 시스템의 감사 정보</t>
+          <t>타병원 진단 후 전원 여부. 코호트 정의 항목이 아니며 필요하면 OBSERVATION 한 개념으로 받는다</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>LYMPHOMA.file_id</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>PET/CT, CT, MRI 또는 병리 이미지 파일의 외래키이다.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>PATHOLOGY_REPORT</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>영상·이미지 파일 참조. 코호트 DB 는 영상 파일을 담지 않는다 (2026-09-21 결정). 담게 되면 IMAGE 확장 표를 둔다</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>MASLD.procedure_occurrence_crtn_dt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>행위처방 데이터 생성일시이다.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>BIOMARKER</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>행위처방 레코드의 생성 일시. 임상 값이 아니라 원천 시스템의 감사 정보</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>COLORECTAL_CANCER.cc_src_spcd</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>주증상 출처(기록지)를 구분하는 코드값이다.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>OBSERVATION</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>주증상을 어느 기록지에서 옮겼는지. OBSERVATION.observation_type_concept_id 가 출처 종류를 맡는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>BREAST_CANCER.file_id</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>이미지 및 영상 파일에 대한 외래키이다.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>BREAST_CRF</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>영상·이미지 파일 참조. 코호트 DB 는 영상 파일을 담지 않는다 (2026-09-21 결정). 담게 되면 IMAGE 확장 표를 둔다</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>MASLD.file_id</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>이미지/영상 파일 ID</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>MASLD_CRF</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>영상·이미지 파일 참조. 코호트 DB 는 영상 파일을 담지 않는다 (2026-09-21 결정). 담게 되면 IMAGE 확장 표를 둔다</t>
         </is>
       </c>
     </row>
